--- a/Week12/Day2/Ex_XP/Movies.xlsx
+++ b/Week12/Day2/Ex_XP/Movies.xlsx
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId3"/>
+    <pivotCache cacheId="13" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25303,7 +25303,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0F7C228-9E9A-B94A-AC7B-FEDBB6C4C30B}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Certificate">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0F7C228-9E9A-B94A-AC7B-FEDBB6C4C30B}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Certificate">
   <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>

--- a/Week12/Day2/Ex_XP/Movies.xlsx
+++ b/Week12/Day2/Ex_XP/Movies.xlsx
@@ -8,22 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AurianeB/DI-Bootcamp/Week12/Day2/Ex_XP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8665D36-89E3-AE4D-BC9A-3ED5389D82C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E331F6-1710-1F49-80B3-A0F1D93E0CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="660" windowWidth="29500" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Oscar_Nominations_Analysis" sheetId="3" r:id="rId1"/>
     <sheet name="Films" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="MovieRange">Films!$A$1:$N$1201</definedName>
+    <definedName name="Slicer_Genre">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId3"/>
+    <pivotCache cacheId="17" r:id="rId3"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId4"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -43,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7815" uniqueCount="1968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7815" uniqueCount="1969">
   <si>
     <t>ID</t>
   </si>
@@ -5946,7 +5955,10 @@
     <t>(All)</t>
   </si>
   <si>
-    <t>Average of Oscar Wins</t>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Average of Nominations</t>
   </si>
 </sst>
 </file>
@@ -5989,7 +6001,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6005,6 +6017,1114 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Movies.xlsx]Oscar_Nominations_Analysis!PivotTable3</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IL" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Average Oscar Nominations by Film Certificate</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-IL"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Oscar_Nominations_Analysis!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Oscar_Nominations_Analysis!$A$4:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>PG</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>U</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Unknown</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Oscar_Nominations_Analysis!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1.5970149253731343</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6962750716332378</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4126984126984128</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.1596958174904941</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.1560283687943262</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-184E-3F4D-BFD9-2ADCC2D6433E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1517694335"/>
+        <c:axId val="1535648959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1517694335"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1535648959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1535648959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1517694335"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-IL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>673100</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7CAEE8C-0BC0-A860-75BA-C72766400443}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Genre">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AC12BD9-16CB-0F49-38B3-DE593769F8AC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Genre"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11226800" y="203200"/>
+              <a:ext cx="1447800" cy="4572000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6091,7 +7211,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="612268957"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -25303,7 +26423,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0F7C228-9E9A-B94A-AC7B-FEDBB6C4C30B}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Certificate">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2BBFD394-C2D4-C349-A26F-F19151360C65}" name="PivotTable3" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -25357,8 +26477,8 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="9"/>
@@ -25396,8 +26516,19 @@
     <pageField fld="4" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Average of Oscar Wins" fld="13" subtotal="average" baseField="0" baseItem="0" numFmtId="1"/>
+    <dataField name="Average of Nominations" fld="12" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
   </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -25408,6 +26539,50 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Genre" xr10:uid="{1CA17D99-749E-824C-B314-A3945133B101}" sourceName="Genre">
+  <pivotTables>
+    <pivotTable tabId="3" name="PivotTable3"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="612268957">
+      <items count="24">
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="7" s="1"/>
+        <i x="19" s="1"/>
+        <i x="12" s="1"/>
+        <i x="3" s="1"/>
+        <i x="11" s="1"/>
+        <i x="20" s="1"/>
+        <i x="18" s="1"/>
+        <i x="13" s="1"/>
+        <i x="23" s="1"/>
+        <i x="6" s="1"/>
+        <i x="15" s="1"/>
+        <i x="8" s="1"/>
+        <i x="14" s="1"/>
+        <i x="21" s="1"/>
+        <i x="10" s="1"/>
+        <i x="2" s="1"/>
+        <i x="22" s="1"/>
+        <i x="5" s="1"/>
+        <i x="17" s="1"/>
+        <i x="9" s="1"/>
+        <i x="4" s="1"/>
+        <i x="16" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Genre" xr10:uid="{28C748F9-B87B-C448-AC2B-7129C272C5C8}" cache="Slicer_Genre" caption="Genre" rowHeight="230716"/>
+</slicers>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25706,12 +26881,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987E6904-ADF7-1241-9D30-EEA85552A7CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86049C79-8E33-444B-A0DE-F28B75229DC3}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -25724,10 +26899,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>1967</v>
       </c>
       <c r="B3" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -25735,7 +26910,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5074626865671642</v>
+        <v>1.5970149253731343</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -25743,7 +26918,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="4">
-        <v>0.50429799426934097</v>
+        <v>1.6962750716332378</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -25751,7 +26926,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="4">
-        <v>0.38095238095238093</v>
+        <v>1.4126984126984128</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -25759,7 +26934,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="4">
-        <v>0.36666666666666664</v>
+        <v>1.2666666666666666</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -25767,7 +26942,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="4">
-        <v>0.74904942965779464</v>
+        <v>2.1596958174904941</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -25775,7 +26950,7 @@
         <v>63</v>
       </c>
       <c r="B9" s="4">
-        <v>0.97872340425531912</v>
+        <v>3.1560283687943262</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -25791,11 +26966,19 @@
         <v>1965</v>
       </c>
       <c r="B11" s="4">
-        <v>0.56916666666666671</v>
+        <v>1.8391666666666666</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
